--- a/output/pdf_financials_xlsx/MRD.xlsx
+++ b/output/pdf_financials_xlsx/MRD.xlsx
@@ -1002,37 +1002,37 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>6.633</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.906</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.514</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>2.318</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>2.309</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>2.812</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>2.427</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1.178</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>1.129</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>1.291</v>
       </c>
     </row>
     <row r="13">
@@ -1871,37 +1871,37 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>51.547</v>
+        <v>44.914</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>31.196</v>
+        <v>29.29</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>74.08</v>
+        <v>71.95</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>102.855</v>
+        <v>100.341</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>134.39</v>
+        <v>132.072</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>119.844</v>
+        <v>117.535</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>123.148</v>
+        <v>120.336</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>100.524</v>
+        <v>98.09699999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>56.975</v>
+        <v>55.797</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>53.685</v>
+        <v>52.556</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>83.241</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="28">
@@ -1981,37 +1981,37 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>51.547</v>
+        <v>44.914</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>31.196</v>
+        <v>29.29</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>74.08</v>
+        <v>71.95</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>102.855</v>
+        <v>100.341</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>134.39</v>
+        <v>132.072</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>119.844</v>
+        <v>117.535</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>123.148</v>
+        <v>120.336</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>100.524</v>
+        <v>98.09699999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>56.975</v>
+        <v>55.797</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>53.685</v>
+        <v>52.556</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>83.241</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="30">
@@ -2036,37 +2036,37 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>47.53679589804124</v>
+        <v>41.41982367479435</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>22.83614429608808</v>
+        <v>21.44091122042633</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>39.00774573352781</v>
+        <v>37.8861677312004</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>46.67822408996637</v>
+        <v>45.53730672705571</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>48.88153348124978</v>
+        <v>48.03840977703415</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>39.45585398133943</v>
+        <v>38.69566935096233</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>39.3432776693322</v>
+        <v>38.44490094534023</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>38.17719865253372</v>
+        <v>37.25546791032589</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>23.498624521057</v>
+        <v>23.01277318826533</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>20.81217290172514</v>
+        <v>20.37449118046133</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>31.12581048034281</v>
+        <v>30.64307455297382</v>
       </c>
     </row>
     <row r="31">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -33160,7 +33160,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -33848,7 +33848,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -33936,7 +33936,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -35038,7 +35038,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -35550,7 +35550,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">

--- a/output/pdf_financials_xlsx/MRD.xlsx
+++ b/output/pdf_financials_xlsx/MRD.xlsx
@@ -1063,31 +1063,31 @@
         <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>10.563</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>13.704</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>14.73</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>15.366</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>16.853</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>23.743</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>25.048</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>20.874</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>22.848</v>
       </c>
     </row>
     <row r="14">
@@ -1877,31 +1877,31 @@
         <v>29.29</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>71.95</v>
+        <v>61.387</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>100.341</v>
+        <v>86.637</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>132.072</v>
+        <v>117.342</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>117.535</v>
+        <v>102.169</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>120.336</v>
+        <v>103.483</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>98.09699999999999</v>
+        <v>74.354</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>55.797</v>
+        <v>30.749</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>52.556</v>
+        <v>31.682</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>81.95</v>
+        <v>59.102</v>
       </c>
     </row>
     <row r="28">
@@ -1932,31 +1932,31 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>1.238</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>1.447</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>1.598</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>1.705</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1.571</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>1.436</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>1.417</v>
       </c>
     </row>
     <row r="29">
@@ -1987,31 +1987,31 @@
         <v>29.29</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>71.95</v>
+        <v>62.647</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>100.341</v>
+        <v>87.75700000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>132.072</v>
+        <v>118.58</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>117.535</v>
+        <v>103.616</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>120.336</v>
+        <v>105.081</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>98.09699999999999</v>
+        <v>76.059</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>55.797</v>
+        <v>32.32</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>52.556</v>
+        <v>33.118</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>81.95</v>
+        <v>60.519</v>
       </c>
     </row>
     <row r="30">
@@ -2042,31 +2042,31 @@
         <v>21.44091122042633</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>37.8861677312004</v>
+        <v>32.98755732948592</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>45.53730672705571</v>
+        <v>39.82636635519108</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>48.03840977703415</v>
+        <v>43.13097879460226</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>38.69566935096233</v>
+        <v>34.11316182813045</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.44490094534023</v>
+        <v>33.57123916564699</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>37.25546791032589</v>
+        <v>28.88583375425831</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>23.01277318826533</v>
+        <v>13.32997884195809</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>20.37449118046133</v>
+        <v>12.83892227175809</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>30.64307455297382</v>
+        <v>22.62950858903505</v>
       </c>
     </row>
     <row r="31">
@@ -5928,31 +5928,31 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>1.238</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.447</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.598</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.705</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.571</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>1.436</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.417</v>
       </c>
     </row>
     <row r="101">
@@ -16888,7 +16888,11 @@
           <t>Depreciation of property and equipment (note 12 and 22)</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19634,7 +19638,11 @@
           <t>Depreciation of property and equipment (note 12 and 23)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -20644,7 +20652,11 @@
           <t>Depreciation of property and equipment (note 11)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -23292,7 +23304,11 @@
           <t>Depreciation of property and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -29784,7 +29800,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -34022,7 +34042,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MRD.xlsx
+++ b/output/pdf_financials_xlsx/MRD.xlsx
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>7.335</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>8.241</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.26</v>
+        <v>9.760999999999999</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>1.12</v>
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>44.914</v>
+        <v>52.249</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>29.29</v>
+        <v>37.531</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>62.647</v>
+        <v>71.148</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>87.75700000000001</v>
@@ -2036,13 +2036,13 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>41.41982367479435</v>
+        <v>48.18418237485706</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>21.44091122042633</v>
+        <v>27.47350081986414</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>32.98755732948592</v>
+        <v>37.46386465238981</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>39.82636635519108</v>
@@ -3465,13 +3465,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>24.856</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>20.723</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>21.268</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
@@ -3483,16 +3483,16 @@
         <v>0</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>30.29</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>31.099</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>31.449</v>
       </c>
     </row>
     <row r="57">
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>5.899</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0</v>
@@ -3538,16 +3538,16 @@
         <v>0</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>14.021</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>15.592</v>
       </c>
       <c r="N57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>17.429</v>
       </c>
     </row>
     <row r="58">
@@ -3948,10 +3948,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>16.402</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>21.674</v>
       </c>
       <c r="O64" s="3" t="n">
         <v>0</v>
@@ -26686,7 +26686,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -35736,7 +35740,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -35753,13 +35761,13 @@
         </is>
       </c>
       <c r="H340" s="5" t="n">
-        <v>-7.335</v>
+        <v>7.335</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>-8.241</v>
+        <v>8.241</v>
       </c>
       <c r="J340" s="5" t="n">
-        <v>-9.760999999999999</v>
+        <v>9.760999999999999</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
